--- a/docs/data/score_table.xlsx
+++ b/docs/data/score_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uscedu-my.sharepoint.com/personal/jnelson4_usc_edu/Documents/Github/website/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{868EB198-DD10-40E3-B126-D630E2FD229B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1116E61B-A026-43B7-97D4-243791B04926}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{868EB198-DD10-40E3-B126-D630E2FD229B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84118521-7C45-4A5E-8AE0-7420115A98CD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{415608D0-703B-3644-9AA1-9DDDDB42A465}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{415608D0-703B-3644-9AA1-9DDDDB42A465}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="50">
   <si>
     <t>Topic</t>
   </si>
@@ -177,6 +177,15 @@
   </si>
   <si>
     <t>SCORE #9</t>
+  </si>
+  <si>
+    <t>March 30th</t>
+  </si>
+  <si>
+    <t>Xenium Explorer to ggplot!</t>
+  </si>
+  <si>
+    <t>SCORE #10</t>
   </si>
 </sst>
 </file>
@@ -575,7 +584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB11DA9E-E571-6D41-AABB-E67CBE5C5423}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
@@ -752,6 +761,20 @@
       </c>
       <c r="E10" s="3" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/score_table.xlsx
+++ b/docs/data/score_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uscedu-my.sharepoint.com/personal/jnelson4_usc_edu/Documents/Github/website/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{868EB198-DD10-40E3-B126-D630E2FD229B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84118521-7C45-4A5E-8AE0-7420115A98CD}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{868EB198-DD10-40E3-B126-D630E2FD229B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AB3ECFC-8B86-4FB5-AB35-58C769CD55F0}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{415608D0-703B-3644-9AA1-9DDDDB42A465}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{415608D0-703B-3644-9AA1-9DDDDB42A465}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
   <si>
     <t>Topic</t>
   </si>
@@ -186,6 +186,9 @@
   </si>
   <si>
     <t>SCORE #10</t>
+  </si>
+  <si>
+    <t>https://usckrc.github.io/website/SCORE_10.html</t>
   </si>
 </sst>
 </file>
@@ -776,6 +779,9 @@
       <c r="D11" s="2" t="s">
         <v>49</v>
       </c>
+      <c r="E11" s="3" t="s">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -786,6 +792,7 @@
     <hyperlink ref="E8" r:id="rId5" xr:uid="{D76BBE40-2AAB-4868-8789-EB5A239F4DCA}"/>
     <hyperlink ref="E9" r:id="rId6" xr:uid="{413AEE38-1F0C-4E3B-A436-A4897DFE3C2D}"/>
     <hyperlink ref="E10" r:id="rId7" xr:uid="{B47E4B98-32B8-47FC-BC0F-24321C75FB0C}"/>
+    <hyperlink ref="E11" r:id="rId8" xr:uid="{EB73AA11-03E7-4659-B967-F4FDFAE874A9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/data/score_table.xlsx
+++ b/docs/data/score_table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uscedu-my.sharepoint.com/personal/jnelson4_usc_edu/Documents/Github/website/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{868EB198-DD10-40E3-B126-D630E2FD229B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AB3ECFC-8B86-4FB5-AB35-58C769CD55F0}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{868EB198-DD10-40E3-B126-D630E2FD229B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C151F4C-01FA-4C07-AE69-A8BC70209FAE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{415608D0-703B-3644-9AA1-9DDDDB42A465}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="55">
   <si>
     <t>Topic</t>
   </si>
@@ -189,13 +189,25 @@
   </si>
   <si>
     <t>https://usckrc.github.io/website/SCORE_10.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ani Solanki </t>
+  </si>
+  <si>
+    <t>SCORE #11</t>
+  </si>
+  <si>
+    <t>June 29th</t>
+  </si>
+  <si>
+    <t>Introducing Atera!</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -225,6 +237,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -247,11 +265,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -587,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB11DA9E-E571-6D41-AABB-E67CBE5C5423}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
@@ -781,6 +800,20 @@
       </c>
       <c r="E11" s="3" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
